--- a/template/template-all-sources.xlsx
+++ b/template/template-all-sources.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="PointSource" sheetId="1" state="visible" r:id="rId2"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="503">
   <si>
     <t xml:space="preserve">facility_id</t>
   </si>
@@ -256,7 +256,7 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">Generalised NFR</t>
+    <t xml:space="preserve">Gridded Nomenclature for Reporting</t>
   </si>
   <si>
     <t xml:space="preserve">GNFR</t>
@@ -286,763 +286,760 @@
     <t xml:space="preserve">vertical_distribution_slug</t>
   </si>
   <si>
-    <t xml:space="preserve">1A1a</t>
+    <t xml:space="preserve">1.A.1.a</t>
   </si>
   <si>
     <t xml:space="preserve">Public electricity and heat production</t>
   </si>
   <si>
-    <t xml:space="preserve">1A1b</t>
+    <t xml:space="preserve">1.A.1.b</t>
   </si>
   <si>
     <t xml:space="preserve">Petroleum refining</t>
   </si>
   <si>
-    <t xml:space="preserve">1A1c</t>
+    <t xml:space="preserve">1.A.1.c</t>
   </si>
   <si>
     <t xml:space="preserve">Manufacture of solid fuels and other energy industries</t>
   </si>
   <si>
-    <t xml:space="preserve">1A2a</t>
+    <t xml:space="preserve">1.A.2.a</t>
   </si>
   <si>
     <t xml:space="preserve">Stationary combustion in manufacturing industries and construction: Iron and steel</t>
   </si>
   <si>
-    <t xml:space="preserve">1A2b</t>
+    <t xml:space="preserve">1.A.2.b</t>
   </si>
   <si>
     <t xml:space="preserve">Stationary combustion in manufacturing industries and construction: Non-ferrous metals</t>
   </si>
   <si>
-    <t xml:space="preserve">1A2c</t>
+    <t xml:space="preserve">1.A.2.c</t>
   </si>
   <si>
     <t xml:space="preserve">Stationary combustion in manufacturing industries and construction: Chemicals</t>
   </si>
   <si>
-    <t xml:space="preserve">1A2d</t>
+    <t xml:space="preserve">1.A.2.d</t>
   </si>
   <si>
     <t xml:space="preserve">Stationary combustion in manufacturing industries and construction: Pulp, Paper and Print</t>
   </si>
   <si>
-    <t xml:space="preserve">1A2e</t>
+    <t xml:space="preserve">1.A.2.e</t>
   </si>
   <si>
     <t xml:space="preserve">Stationary combustion in manufacturing industries and construction: Food processing, beverages and tobacco</t>
   </si>
   <si>
-    <t xml:space="preserve">1A2f</t>
+    <t xml:space="preserve">1.A.2.f</t>
   </si>
   <si>
     <t xml:space="preserve">Stationary combustion in manufacturing industries and construction: Non-metallic minerals</t>
   </si>
   <si>
-    <t xml:space="preserve">1A2gvii</t>
+    <t xml:space="preserve">1.A.2.g.vii</t>
   </si>
   <si>
     <t xml:space="preserve">Mobile combustion in manufacturing industries and construction (please specify in the IIR)</t>
   </si>
   <si>
-    <t xml:space="preserve">1A2gviii</t>
+    <t xml:space="preserve">1.A.2.g.viii</t>
   </si>
   <si>
     <t xml:space="preserve">Stationary combustion in manufacturing industries and construction: Other (please specify in the IIR)</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3ai(i)</t>
+    <t xml:space="preserve">1.A.3.a.i.(i)</t>
   </si>
   <si>
     <t xml:space="preserve">International aviation LTO (civil)</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3aii(i)</t>
+    <t xml:space="preserve">1.A.3.a.ii.(i)</t>
   </si>
   <si>
     <t xml:space="preserve">Domestic aviation LTO (civil)</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3bi</t>
+    <t xml:space="preserve">1.A.3.b.i</t>
   </si>
   <si>
     <t xml:space="preserve">Road transport: Passenger cars</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3bii</t>
+    <t xml:space="preserve">1.A.3.b.ii</t>
   </si>
   <si>
     <t xml:space="preserve">Road transport: Light duty vehicles</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3biii</t>
+    <t xml:space="preserve">1.A.3.b.iii</t>
   </si>
   <si>
     <t xml:space="preserve">Road transport: Heavy duty vehicles and buses</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3biv</t>
+    <t xml:space="preserve">1.A.3.b.iv</t>
   </si>
   <si>
     <t xml:space="preserve">Road transport: Mopeds &amp; motorcycles</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3bv</t>
+    <t xml:space="preserve">1.A.3.b.v</t>
   </si>
   <si>
     <t xml:space="preserve">Road transport: Gasoline evaporation</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3bvi</t>
+    <t xml:space="preserve">1.A.3.b.vi</t>
   </si>
   <si>
     <t xml:space="preserve">Road transport: Automobile tyre and brake wear</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3bvii</t>
+    <t xml:space="preserve">1.A.3.b.vii</t>
   </si>
   <si>
     <t xml:space="preserve">Road transport: Automobile road abrasion</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3c</t>
+    <t xml:space="preserve">1.A.3.c</t>
   </si>
   <si>
     <t xml:space="preserve">Railways</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3di(ii)</t>
+    <t xml:space="preserve">1.A.3.d.i(ii)</t>
   </si>
   <si>
     <t xml:space="preserve">International inland waterways</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3dii</t>
+    <t xml:space="preserve">1.A.3.d.ii</t>
   </si>
   <si>
     <t xml:space="preserve">National navigation (shipping)</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3ei</t>
+    <t xml:space="preserve">1.A.3.e.i</t>
   </si>
   <si>
     <t xml:space="preserve">Pipeline transport</t>
   </si>
   <si>
-    <t xml:space="preserve">1A3eii</t>
+    <t xml:space="preserve">1.A.3.e.ii</t>
   </si>
   <si>
     <t xml:space="preserve">Other</t>
   </si>
   <si>
-    <t xml:space="preserve">1A4ai</t>
+    <t xml:space="preserve">1.A.4.a.i</t>
   </si>
   <si>
     <t xml:space="preserve">Commercial/Institutional: Stationary</t>
   </si>
   <si>
-    <t xml:space="preserve">1A4aii</t>
+    <t xml:space="preserve">1.A.4.a.ii</t>
   </si>
   <si>
     <t xml:space="preserve">Commercial/Institutional: Mobile</t>
   </si>
   <si>
-    <t xml:space="preserve">1A4bi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Residential: Stationary</t>
   </si>
   <si>
-    <t xml:space="preserve">1A4bii</t>
+    <t xml:space="preserve">1.A.4.b.ii</t>
   </si>
   <si>
     <t xml:space="preserve">Residential: Household and gardening (mobile)</t>
   </si>
   <si>
-    <t xml:space="preserve">1A4ci</t>
+    <t xml:space="preserve">1.A.4.c.i</t>
   </si>
   <si>
     <t xml:space="preserve">Agriculture/Forestry/Fishing: Stationary</t>
   </si>
   <si>
-    <t xml:space="preserve">1A4cii</t>
+    <t xml:space="preserve">1.A.4.c.ii</t>
   </si>
   <si>
     <t xml:space="preserve">Agriculture/Forestry/Fishing: Off-road vehicles and other machinery</t>
   </si>
   <si>
-    <t xml:space="preserve">1A4ciii</t>
+    <t xml:space="preserve">1.A.4.c.iii</t>
   </si>
   <si>
     <t xml:space="preserve">Agriculture/Forestry/Fishing: National fishing</t>
   </si>
   <si>
-    <t xml:space="preserve">1A5a</t>
+    <t xml:space="preserve">1.A.5.a</t>
   </si>
   <si>
     <t xml:space="preserve">Other stationary (including military)</t>
   </si>
   <si>
-    <t xml:space="preserve">1A5b</t>
+    <t xml:space="preserve">1.A.5.b</t>
   </si>
   <si>
     <t xml:space="preserve">Other, Mobile (including military, land based and recreational boats)</t>
   </si>
   <si>
-    <t xml:space="preserve">1B1a</t>
+    <t xml:space="preserve">1.B.1.a</t>
   </si>
   <si>
     <t xml:space="preserve">Fugitive emission from solid fuels: Coal mining and handling</t>
   </si>
   <si>
-    <t xml:space="preserve">1B1b</t>
+    <t xml:space="preserve">1.B.1.b</t>
   </si>
   <si>
     <t xml:space="preserve">Fugitive emission from solid fuels: Solid fuel transformation</t>
   </si>
   <si>
-    <t xml:space="preserve">1B1c</t>
+    <t xml:space="preserve">1.B.1.c</t>
   </si>
   <si>
     <t xml:space="preserve">Other fugitive emissions from solid fuels</t>
   </si>
   <si>
-    <t xml:space="preserve">1B2ai</t>
+    <t xml:space="preserve">1.B.2.a.i</t>
   </si>
   <si>
     <t xml:space="preserve">Fugitive emissions oil: Exploration, production, transport</t>
   </si>
   <si>
-    <t xml:space="preserve">1B2aiv</t>
+    <t xml:space="preserve">1.B.2.a.iv</t>
   </si>
   <si>
     <t xml:space="preserve">Fugitive emissions oil: Refining and storage</t>
   </si>
   <si>
-    <t xml:space="preserve">1B2av</t>
+    <t xml:space="preserve">1.B.2.a.v</t>
   </si>
   <si>
     <t xml:space="preserve">Distribution of oil products</t>
   </si>
   <si>
-    <t xml:space="preserve">1B2b</t>
+    <t xml:space="preserve">1.B.2.b</t>
   </si>
   <si>
     <t xml:space="preserve">Fugitive emissions from natural gas (exploration, production, processing, transmission, storage, distribution and other)</t>
   </si>
   <si>
-    <t xml:space="preserve">1B2c</t>
+    <t xml:space="preserve">1.B.2.c</t>
   </si>
   <si>
     <t xml:space="preserve">Venting and flaring (oil, gas, combined oil and gas)</t>
   </si>
   <si>
-    <t xml:space="preserve">1B2d</t>
+    <t xml:space="preserve">1.B.2.d</t>
   </si>
   <si>
     <t xml:space="preserve">Other fugitive emissions from energy production</t>
   </si>
   <si>
-    <t xml:space="preserve">2A1</t>
+    <t xml:space="preserve">2.A.1</t>
   </si>
   <si>
     <t xml:space="preserve">Cement production</t>
   </si>
   <si>
-    <t xml:space="preserve">2A2</t>
+    <t xml:space="preserve">2.A.2</t>
   </si>
   <si>
     <t xml:space="preserve">Lime production</t>
   </si>
   <si>
-    <t xml:space="preserve">2A3</t>
+    <t xml:space="preserve">2.A.3</t>
   </si>
   <si>
     <t xml:space="preserve">Glass production</t>
   </si>
   <si>
-    <t xml:space="preserve">2A5a</t>
+    <t xml:space="preserve">2.A.5.a</t>
   </si>
   <si>
     <t xml:space="preserve">Quarrying and mining of minerals other than coal</t>
   </si>
   <si>
-    <t xml:space="preserve">2A5b</t>
+    <t xml:space="preserve">2.A.5.b</t>
   </si>
   <si>
     <t xml:space="preserve">Construction and demolition</t>
   </si>
   <si>
-    <t xml:space="preserve">2A5c</t>
+    <t xml:space="preserve">2.A.5.c</t>
   </si>
   <si>
     <t xml:space="preserve">Storage, handling and transport of mineral products</t>
   </si>
   <si>
-    <t xml:space="preserve">2A6</t>
+    <t xml:space="preserve">2.A.6</t>
   </si>
   <si>
     <t xml:space="preserve">Other mineral products</t>
   </si>
   <si>
-    <t xml:space="preserve">2B1</t>
+    <t xml:space="preserve">2.B.1</t>
   </si>
   <si>
     <t xml:space="preserve">Ammonia production</t>
   </si>
   <si>
-    <t xml:space="preserve">2B2</t>
+    <t xml:space="preserve">2.B.2</t>
   </si>
   <si>
     <t xml:space="preserve">Nitric acid production</t>
   </si>
   <si>
-    <t xml:space="preserve">2B3</t>
+    <t xml:space="preserve">2.B.3</t>
   </si>
   <si>
     <t xml:space="preserve">Adipic acid production</t>
   </si>
   <si>
-    <t xml:space="preserve">2B5</t>
+    <t xml:space="preserve">2.B.5</t>
   </si>
   <si>
     <t xml:space="preserve">Carbide production</t>
   </si>
   <si>
-    <t xml:space="preserve">2B6</t>
+    <t xml:space="preserve">2.B.6</t>
   </si>
   <si>
     <t xml:space="preserve">Titanium dioxide production</t>
   </si>
   <si>
-    <t xml:space="preserve">2B7</t>
+    <t xml:space="preserve">2.B.7</t>
   </si>
   <si>
     <t xml:space="preserve">Soda ash production</t>
   </si>
   <si>
-    <t xml:space="preserve">2B10a</t>
+    <t xml:space="preserve">2.B.10.a</t>
   </si>
   <si>
     <t xml:space="preserve">Chemical industry: Other</t>
   </si>
   <si>
-    <t xml:space="preserve">2B10b</t>
+    <t xml:space="preserve">2.B.10.b</t>
   </si>
   <si>
     <t xml:space="preserve">Storage, handling and transport of chemical products</t>
   </si>
   <si>
-    <t xml:space="preserve">2C1</t>
+    <t xml:space="preserve">2.C.1</t>
   </si>
   <si>
     <t xml:space="preserve">Iron and steel production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C2</t>
+    <t xml:space="preserve">2.C.2</t>
   </si>
   <si>
     <t xml:space="preserve">Ferroalloys production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C3</t>
+    <t xml:space="preserve">2.C.3</t>
   </si>
   <si>
     <t xml:space="preserve">Aluminium production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C4</t>
+    <t xml:space="preserve">2.C.4</t>
   </si>
   <si>
     <t xml:space="preserve">Magnesium production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C5</t>
+    <t xml:space="preserve">2.C.5</t>
   </si>
   <si>
     <t xml:space="preserve">Lead production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C6</t>
+    <t xml:space="preserve">2.C.6</t>
   </si>
   <si>
     <t xml:space="preserve">Zinc production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C7a</t>
+    <t xml:space="preserve">2.C.7.a</t>
   </si>
   <si>
     <t xml:space="preserve">Copper production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C7b</t>
+    <t xml:space="preserve">2.C.7.b</t>
   </si>
   <si>
     <t xml:space="preserve">Nickel production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C7c</t>
+    <t xml:space="preserve">2.C.7.c</t>
   </si>
   <si>
     <t xml:space="preserve">Other metal production</t>
   </si>
   <si>
-    <t xml:space="preserve">2C7d</t>
+    <t xml:space="preserve">2.C.7.d</t>
   </si>
   <si>
     <t xml:space="preserve">Storage, handling and transport of metal products</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3a</t>
+    <t xml:space="preserve">2.D.3.a</t>
   </si>
   <si>
     <t xml:space="preserve">Domestic solvent use including fungicides</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3b</t>
+    <t xml:space="preserve">2.D.3.b</t>
   </si>
   <si>
     <t xml:space="preserve">Road paving with asphalt</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3c</t>
+    <t xml:space="preserve">2.D.3.c</t>
   </si>
   <si>
     <t xml:space="preserve">Asphalt roofing</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3d</t>
+    <t xml:space="preserve">2.D.3.d</t>
   </si>
   <si>
     <t xml:space="preserve">Coating applications</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3e</t>
+    <t xml:space="preserve">2.D.3.e</t>
   </si>
   <si>
     <t xml:space="preserve">Degreasing</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3f</t>
+    <t xml:space="preserve">2.D.3.f</t>
   </si>
   <si>
     <t xml:space="preserve">Dry cleaning</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3g</t>
+    <t xml:space="preserve">2.D.3.g</t>
   </si>
   <si>
     <t xml:space="preserve">Chemical products</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3h</t>
+    <t xml:space="preserve">2.D.3.h</t>
   </si>
   <si>
     <t xml:space="preserve">Printing</t>
   </si>
   <si>
-    <t xml:space="preserve">2D3i</t>
+    <t xml:space="preserve">2.D.3.i</t>
   </si>
   <si>
     <t xml:space="preserve">Other solvent use</t>
   </si>
   <si>
-    <t xml:space="preserve">2G</t>
+    <t xml:space="preserve">2.G</t>
   </si>
   <si>
     <t xml:space="preserve">Other product use</t>
   </si>
   <si>
-    <t xml:space="preserve">2H1</t>
+    <t xml:space="preserve">2.H.1</t>
   </si>
   <si>
     <t xml:space="preserve">Pulp and paper industry</t>
   </si>
   <si>
-    <t xml:space="preserve">2H2</t>
+    <t xml:space="preserve">2.H.2</t>
   </si>
   <si>
     <t xml:space="preserve">Food and beverages industry</t>
   </si>
   <si>
-    <t xml:space="preserve">2H3</t>
+    <t xml:space="preserve">2.H.3</t>
   </si>
   <si>
     <t xml:space="preserve">Other industrial processes</t>
   </si>
   <si>
-    <t xml:space="preserve">2I</t>
+    <t xml:space="preserve">2.I</t>
   </si>
   <si>
     <t xml:space="preserve">Wood processing</t>
   </si>
   <si>
-    <t xml:space="preserve">2J</t>
+    <t xml:space="preserve">2.J</t>
   </si>
   <si>
     <t xml:space="preserve">Production of POPs</t>
   </si>
   <si>
-    <t xml:space="preserve">2K</t>
+    <t xml:space="preserve">2.K</t>
   </si>
   <si>
     <t xml:space="preserve">Consumption of POPs and heavy metals (e.g. electrical and scientific equipment)</t>
   </si>
   <si>
-    <t xml:space="preserve">2L</t>
+    <t xml:space="preserve">2.L</t>
   </si>
   <si>
     <t xml:space="preserve">Other production, consumption, storage, transportation or handling of bulk products</t>
   </si>
   <si>
-    <t xml:space="preserve">3B1a</t>
+    <t xml:space="preserve">3.B.1.a</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Dairy cattle</t>
   </si>
   <si>
-    <t xml:space="preserve">3B1b</t>
+    <t xml:space="preserve">3.B.1.b</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Non-dairy cattle</t>
   </si>
   <si>
-    <t xml:space="preserve">3B2</t>
+    <t xml:space="preserve">3.B.2</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Sheep</t>
   </si>
   <si>
-    <t xml:space="preserve">3B3</t>
+    <t xml:space="preserve">3.B.3</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Swine</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4a</t>
+    <t xml:space="preserve">3.B.4.a</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Buffalo</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4d</t>
+    <t xml:space="preserve">3.B.4.d</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Goats</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4e</t>
+    <t xml:space="preserve">3.B.4.e</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Horses</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4f</t>
+    <t xml:space="preserve">3.B.4.f</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Mules and asses</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4gi</t>
+    <t xml:space="preserve">3.B.4.g.i</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Laying hens</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4gii</t>
+    <t xml:space="preserve">3.B.4.g.ii</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Broilers</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4giii</t>
+    <t xml:space="preserve">3.B.4.g.iii</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Turkeys</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4giv</t>
+    <t xml:space="preserve">3.B.4.g.iv</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Other poultry</t>
   </si>
   <si>
-    <t xml:space="preserve">3B4h</t>
+    <t xml:space="preserve">3.B.4.h</t>
   </si>
   <si>
     <t xml:space="preserve">Manure management - Other animals</t>
   </si>
   <si>
-    <t xml:space="preserve">3Da1</t>
+    <t xml:space="preserve">3.D.a.1</t>
   </si>
   <si>
     <t xml:space="preserve">Inorganic N-fertilizers (includes also urea application)</t>
   </si>
   <si>
-    <t xml:space="preserve">3Da2a</t>
+    <t xml:space="preserve">3.D.a.2.a</t>
   </si>
   <si>
     <t xml:space="preserve">Animal manure applied to soils</t>
   </si>
   <si>
-    <t xml:space="preserve">3Da2b</t>
+    <t xml:space="preserve">3.D.a.2.b</t>
   </si>
   <si>
     <t xml:space="preserve">Sewage sludge applied to soils</t>
   </si>
   <si>
-    <t xml:space="preserve">3Da2c</t>
+    <t xml:space="preserve">3.D.a.2.c</t>
   </si>
   <si>
     <t xml:space="preserve">Other organic fertilisers applied to soils (including compost)</t>
   </si>
   <si>
-    <t xml:space="preserve">3Da3</t>
+    <t xml:space="preserve">3.D.a.3</t>
   </si>
   <si>
     <t xml:space="preserve">Urine and dung deposited by grazing animals</t>
   </si>
   <si>
-    <t xml:space="preserve">3Da4</t>
+    <t xml:space="preserve">3.D.a.4</t>
   </si>
   <si>
     <t xml:space="preserve">Crop residues applied to soils</t>
   </si>
   <si>
-    <t xml:space="preserve">3Db</t>
+    <t xml:space="preserve">3.D.b</t>
   </si>
   <si>
     <t xml:space="preserve">Indirect emissions from managed soils</t>
   </si>
   <si>
-    <t xml:space="preserve">3Dc</t>
+    <t xml:space="preserve">3.D.c</t>
   </si>
   <si>
     <t xml:space="preserve">Farm-level agricultural operations including storage, handling and transport of agricultural products</t>
   </si>
   <si>
-    <t xml:space="preserve">3Dd</t>
+    <t xml:space="preserve">3.D.d</t>
   </si>
   <si>
     <t xml:space="preserve">Off-farm storage, handling and transport of bulk agricultural products</t>
   </si>
   <si>
-    <t xml:space="preserve">3De</t>
+    <t xml:space="preserve">3.D.e</t>
   </si>
   <si>
     <t xml:space="preserve">Cultivated crops</t>
   </si>
   <si>
-    <t xml:space="preserve">3Df</t>
+    <t xml:space="preserve">3.D.f</t>
   </si>
   <si>
     <t xml:space="preserve">Use of pesticides</t>
   </si>
   <si>
-    <t xml:space="preserve">3F</t>
+    <t xml:space="preserve">3.F</t>
   </si>
   <si>
     <t xml:space="preserve">Field burning of agricultural residues</t>
   </si>
   <si>
-    <t xml:space="preserve">3I</t>
+    <t xml:space="preserve">3.I</t>
   </si>
   <si>
     <t xml:space="preserve">Agriculture other</t>
   </si>
   <si>
-    <t xml:space="preserve">5A</t>
+    <t xml:space="preserve">5.A</t>
   </si>
   <si>
     <t xml:space="preserve">Biological treatment of waste - Solid waste disposal on land</t>
   </si>
   <si>
-    <t xml:space="preserve">5B1</t>
+    <t xml:space="preserve">5.B.1</t>
   </si>
   <si>
     <t xml:space="preserve">Biological treatment of waste - Composting</t>
   </si>
   <si>
-    <t xml:space="preserve">5B2</t>
+    <t xml:space="preserve">5.B.2</t>
   </si>
   <si>
     <t xml:space="preserve">Biological treatment of waste - Anaerobic digestion at biogas facilities</t>
   </si>
   <si>
-    <t xml:space="preserve">5C1a</t>
+    <t xml:space="preserve">5.C.1.a</t>
   </si>
   <si>
     <t xml:space="preserve">Municipal waste incineration</t>
   </si>
   <si>
-    <t xml:space="preserve">5C1bi</t>
+    <t xml:space="preserve">5.C.1.b.i</t>
   </si>
   <si>
     <t xml:space="preserve">Industrial waste incineration</t>
   </si>
   <si>
-    <t xml:space="preserve">5C1bii</t>
+    <t xml:space="preserve">5.C.1.b.ii</t>
   </si>
   <si>
     <t xml:space="preserve">Hazardous waste incineration</t>
   </si>
   <si>
-    <t xml:space="preserve">5C1biii</t>
+    <t xml:space="preserve">5.C.1.b.iii</t>
   </si>
   <si>
     <t xml:space="preserve">Clinical waste incineration</t>
   </si>
   <si>
-    <t xml:space="preserve">5C1biv</t>
+    <t xml:space="preserve">5.C.1.b.iv</t>
   </si>
   <si>
     <t xml:space="preserve">Sewage sludge incineration</t>
   </si>
   <si>
-    <t xml:space="preserve">5C1bv</t>
+    <t xml:space="preserve">5.C.1.b.v</t>
   </si>
   <si>
     <t xml:space="preserve">Cremation</t>
   </si>
   <si>
-    <t xml:space="preserve">5C1bvi</t>
+    <t xml:space="preserve">5.C.1.b.vi</t>
   </si>
   <si>
     <t xml:space="preserve">Other waste incineration</t>
   </si>
   <si>
-    <t xml:space="preserve">5C2</t>
+    <t xml:space="preserve">5.C.2</t>
   </si>
   <si>
     <t xml:space="preserve">Open burning of waste</t>
   </si>
   <si>
-    <t xml:space="preserve">5D1</t>
+    <t xml:space="preserve">5.D.1</t>
   </si>
   <si>
     <t xml:space="preserve">Domestic wastewater handling</t>
   </si>
   <si>
-    <t xml:space="preserve">5D2</t>
+    <t xml:space="preserve">5.D.2</t>
   </si>
   <si>
     <t xml:space="preserve">Industrial wastewater handling</t>
   </si>
   <si>
-    <t xml:space="preserve">5D3</t>
+    <t xml:space="preserve">5.D.3</t>
   </si>
   <si>
     <t xml:space="preserve">Other wastewater handling</t>
   </si>
   <si>
-    <t xml:space="preserve">5E</t>
+    <t xml:space="preserve">5.E</t>
   </si>
   <si>
     <t xml:space="preserve">Other waste</t>
   </si>
   <si>
-    <t xml:space="preserve">6A</t>
+    <t xml:space="preserve">6.A</t>
   </si>
   <si>
     <t xml:space="preserve">Other (included in national total for entire territory)</t>
@@ -1051,49 +1048,94 @@
     <t xml:space="preserve">A_PublicPower</t>
   </si>
   <si>
+    <t xml:space="preserve">PublicPower</t>
+  </si>
+  <si>
     <t xml:space="preserve">B_Industry</t>
   </si>
   <si>
+    <t xml:space="preserve">Industry</t>
+  </si>
+  <si>
     <t xml:space="preserve">C_OtherStationaryComb</t>
   </si>
   <si>
+    <t xml:space="preserve">OtherStationaryComb</t>
+  </si>
+  <si>
     <t xml:space="preserve">D_Fugitive</t>
   </si>
   <si>
+    <t xml:space="preserve">Fugitive</t>
+  </si>
+  <si>
     <t xml:space="preserve">E_Solvents</t>
   </si>
   <si>
+    <t xml:space="preserve">Solvents</t>
+  </si>
+  <si>
     <t xml:space="preserve">F_RoadTransport</t>
   </si>
   <si>
+    <t xml:space="preserve">RoadTransport</t>
+  </si>
+  <si>
     <t xml:space="preserve">G_Shipping</t>
   </si>
   <si>
+    <t xml:space="preserve">Shipping</t>
+  </si>
+  <si>
     <t xml:space="preserve">H_Aviation</t>
   </si>
   <si>
+    <t xml:space="preserve">Aviation</t>
+  </si>
+  <si>
     <t xml:space="preserve">I_Offroad</t>
   </si>
   <si>
+    <t xml:space="preserve">Offroad</t>
+  </si>
+  <si>
     <t xml:space="preserve">J_Waste</t>
   </si>
   <si>
+    <t xml:space="preserve">Waste</t>
+  </si>
+  <si>
     <t xml:space="preserve">K_AgriLivestock</t>
   </si>
   <si>
+    <t xml:space="preserve">AgriLivestock</t>
+  </si>
+  <si>
     <t xml:space="preserve">L_AgriOther</t>
   </si>
   <si>
+    <t xml:space="preserve">AgriOther</t>
+  </si>
+  <si>
     <t xml:space="preserve">M_Other</t>
   </si>
   <si>
     <t xml:space="preserve">N_Natural</t>
   </si>
   <si>
+    <t xml:space="preserve">Natural</t>
+  </si>
+  <si>
     <t xml:space="preserve">O_AviationCruise</t>
   </si>
   <si>
+    <t xml:space="preserve">AviationCruise</t>
+  </si>
+  <si>
     <t xml:space="preserve">P_IntShipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntShipping</t>
   </si>
   <si>
     <t xml:space="preserve">01</t>
@@ -1609,7 +1651,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:T5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1917,43 +1959,43 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I50"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -1979,7 +2021,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>1</v>
@@ -2005,7 +2047,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -2031,7 +2073,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>1</v>
@@ -2057,7 +2099,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>1</v>
@@ -2083,7 +2125,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>1</v>
@@ -2109,7 +2151,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>1</v>
@@ -2135,7 +2177,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>1</v>
@@ -2161,7 +2203,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>1</v>
@@ -2187,7 +2229,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>1</v>
@@ -2213,7 +2255,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>1</v>
@@ -2239,7 +2281,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>1</v>
@@ -2265,7 +2307,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>1</v>
@@ -2291,7 +2333,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>1</v>
@@ -2317,7 +2359,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>1</v>
@@ -2343,7 +2385,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>1</v>
@@ -2369,7 +2411,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>1</v>
@@ -2395,7 +2437,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>1</v>
@@ -2421,7 +2463,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>1</v>
@@ -2447,7 +2489,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>1</v>
@@ -2473,7 +2515,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>1</v>
@@ -2499,7 +2541,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>1</v>
@@ -2525,7 +2567,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>1</v>
@@ -2551,7 +2593,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>1</v>
@@ -2577,39 +2619,39 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>1</v>
@@ -2635,7 +2677,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>1</v>
@@ -2661,7 +2703,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>1</v>
@@ -2687,7 +2729,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>1</v>
@@ -2713,7 +2755,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>1</v>
@@ -2739,7 +2781,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>1</v>
@@ -2765,7 +2807,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>1</v>
@@ -2791,7 +2833,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>2</v>
@@ -2817,7 +2859,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>3</v>
@@ -2843,7 +2885,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>4</v>
@@ -2869,7 +2911,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>4</v>
@@ -2895,7 +2937,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>3</v>
@@ -2921,7 +2963,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>2</v>
@@ -2947,7 +2989,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>2</v>
@@ -2973,7 +3015,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="1" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>2</v>
@@ -2999,7 +3041,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>3</v>
@@ -3025,7 +3067,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="1" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>4</v>
@@ -3051,7 +3093,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="1" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>4</v>
@@ -3077,7 +3119,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>4</v>
@@ -3103,7 +3145,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>3</v>
@@ -3129,7 +3171,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>2</v>
@@ -3155,7 +3197,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>1</v>
@@ -3181,7 +3223,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="1" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>1</v>
@@ -3207,7 +3249,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="1" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>1</v>
@@ -3248,88 +3290,88 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3391,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3361,18 +3403,18 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -3392,20 +3434,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -3419,82 +3461,82 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3514,46 +3556,46 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0.9</v>
@@ -3562,10 +3604,10 @@
         <v>0.27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>0.7</v>
@@ -3576,13 +3618,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>0.1</v>
@@ -3591,10 +3633,10 @@
         <v>0.27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>1</v>
@@ -3602,13 +3644,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -3617,10 +3659,10 @@
         <v>0.27</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>1</v>
@@ -3628,13 +3670,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>1</v>
@@ -3643,10 +3685,10 @@
         <v>0.07</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0.7</v>
@@ -3672,215 +3714,215 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -3900,52 +3942,52 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1E-007</v>
@@ -3963,21 +4005,21 @@
         <v>1E-008</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>1E-007</v>
@@ -3995,21 +4037,21 @@
         <v>1E-008</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1E-007</v>
@@ -4027,21 +4069,21 @@
         <v>1E-008</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>1E-007</v>
@@ -4059,21 +4101,21 @@
         <v>1E-008</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1E-007</v>
@@ -4091,21 +4133,21 @@
         <v>1E-008</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>1E-007</v>
@@ -4123,7 +4165,7 @@
         <v>1E-008</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -4143,7 +4185,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -4346,7 +4388,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -4507,7 +4549,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -4610,8 +4652,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="47.8"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -4624,8 +4669,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -4648,6 +4693,7 @@
         <v>78</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4665,15 +4711,15 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D155"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="31.12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
@@ -4989,10 +5035,10 @@
         <v>78</v>
       </c>
       <c r="B29" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="0" t="s">
         <v>137</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5000,10 +5046,10 @@
         <v>78</v>
       </c>
       <c r="B30" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="0" t="s">
         <v>139</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5011,10 +5057,10 @@
         <v>78</v>
       </c>
       <c r="B31" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="0" t="s">
         <v>141</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5022,10 +5068,10 @@
         <v>78</v>
       </c>
       <c r="B32" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="0" t="s">
         <v>143</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5033,10 +5079,10 @@
         <v>78</v>
       </c>
       <c r="B33" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="0" t="s">
         <v>145</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5044,10 +5090,10 @@
         <v>78</v>
       </c>
       <c r="B34" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="0" t="s">
         <v>147</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5055,10 +5101,10 @@
         <v>78</v>
       </c>
       <c r="B35" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="0" t="s">
         <v>149</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5066,10 +5112,10 @@
         <v>78</v>
       </c>
       <c r="B36" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="0" t="s">
         <v>151</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5077,10 +5123,10 @@
         <v>78</v>
       </c>
       <c r="B37" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="C37" s="0" t="s">
         <v>153</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5088,10 +5134,10 @@
         <v>78</v>
       </c>
       <c r="B38" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C38" s="0" t="s">
         <v>155</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5099,10 +5145,10 @@
         <v>78</v>
       </c>
       <c r="B39" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="0" t="s">
         <v>157</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5110,10 +5156,10 @@
         <v>78</v>
       </c>
       <c r="B40" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="C40" s="0" t="s">
         <v>159</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5121,10 +5167,10 @@
         <v>78</v>
       </c>
       <c r="B41" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="0" t="s">
         <v>161</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5132,10 +5178,10 @@
         <v>78</v>
       </c>
       <c r="B42" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="0" t="s">
         <v>163</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5143,10 +5189,10 @@
         <v>78</v>
       </c>
       <c r="B43" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="C43" s="0" t="s">
         <v>165</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5154,10 +5200,10 @@
         <v>78</v>
       </c>
       <c r="B44" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="0" t="s">
         <v>167</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5165,10 +5211,10 @@
         <v>78</v>
       </c>
       <c r="B45" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" s="0" t="s">
         <v>169</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5176,10 +5222,10 @@
         <v>78</v>
       </c>
       <c r="B46" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C46" s="0" t="s">
         <v>171</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5187,10 +5233,10 @@
         <v>78</v>
       </c>
       <c r="B47" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="C47" s="0" t="s">
         <v>173</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5198,10 +5244,10 @@
         <v>78</v>
       </c>
       <c r="B48" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="0" t="s">
         <v>175</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5209,10 +5255,10 @@
         <v>78</v>
       </c>
       <c r="B49" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" s="0" t="s">
         <v>177</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5220,10 +5266,10 @@
         <v>78</v>
       </c>
       <c r="B50" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" s="0" t="s">
         <v>179</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5231,10 +5277,10 @@
         <v>78</v>
       </c>
       <c r="B51" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="C51" s="0" t="s">
         <v>181</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5242,10 +5288,10 @@
         <v>78</v>
       </c>
       <c r="B52" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C52" s="0" t="s">
         <v>183</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5253,10 +5299,10 @@
         <v>78</v>
       </c>
       <c r="B53" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="0" t="s">
         <v>185</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5264,10 +5310,10 @@
         <v>78</v>
       </c>
       <c r="B54" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="C54" s="0" t="s">
         <v>187</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5275,10 +5321,10 @@
         <v>78</v>
       </c>
       <c r="B55" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="C55" s="0" t="s">
         <v>189</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5286,10 +5332,10 @@
         <v>78</v>
       </c>
       <c r="B56" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="C56" s="0" t="s">
         <v>191</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5297,10 +5343,10 @@
         <v>78</v>
       </c>
       <c r="B57" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C57" s="0" t="s">
         <v>193</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5308,10 +5354,10 @@
         <v>78</v>
       </c>
       <c r="B58" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="C58" s="0" t="s">
         <v>195</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5319,10 +5365,10 @@
         <v>78</v>
       </c>
       <c r="B59" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="C59" s="0" t="s">
         <v>197</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5330,10 +5376,10 @@
         <v>78</v>
       </c>
       <c r="B60" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="C60" s="0" t="s">
         <v>199</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5341,10 +5387,10 @@
         <v>78</v>
       </c>
       <c r="B61" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="C61" s="0" t="s">
         <v>201</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5352,10 +5398,10 @@
         <v>78</v>
       </c>
       <c r="B62" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="C62" s="0" t="s">
         <v>203</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5363,10 +5409,10 @@
         <v>78</v>
       </c>
       <c r="B63" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" s="0" t="s">
         <v>205</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5374,10 +5420,10 @@
         <v>78</v>
       </c>
       <c r="B64" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="C64" s="0" t="s">
         <v>207</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5385,10 +5431,10 @@
         <v>78</v>
       </c>
       <c r="B65" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" s="0" t="s">
         <v>209</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5396,10 +5442,10 @@
         <v>78</v>
       </c>
       <c r="B66" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="C66" s="0" t="s">
         <v>211</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5407,10 +5453,10 @@
         <v>78</v>
       </c>
       <c r="B67" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="C67" s="0" t="s">
         <v>213</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5418,10 +5464,10 @@
         <v>78</v>
       </c>
       <c r="B68" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="C68" s="0" t="s">
         <v>215</v>
-      </c>
-      <c r="C68" s="0" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5429,10 +5475,10 @@
         <v>78</v>
       </c>
       <c r="B69" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="C69" s="0" t="s">
         <v>217</v>
-      </c>
-      <c r="C69" s="0" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5440,10 +5486,10 @@
         <v>78</v>
       </c>
       <c r="B70" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="C70" s="0" t="s">
         <v>219</v>
-      </c>
-      <c r="C70" s="0" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5451,10 +5497,10 @@
         <v>78</v>
       </c>
       <c r="B71" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="C71" s="0" t="s">
         <v>221</v>
-      </c>
-      <c r="C71" s="0" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5462,10 +5508,10 @@
         <v>78</v>
       </c>
       <c r="B72" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="C72" s="0" t="s">
         <v>223</v>
-      </c>
-      <c r="C72" s="0" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5473,10 +5519,10 @@
         <v>78</v>
       </c>
       <c r="B73" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="C73" s="0" t="s">
         <v>225</v>
-      </c>
-      <c r="C73" s="0" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5484,10 +5530,10 @@
         <v>78</v>
       </c>
       <c r="B74" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="C74" s="0" t="s">
         <v>227</v>
-      </c>
-      <c r="C74" s="0" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5495,10 +5541,10 @@
         <v>78</v>
       </c>
       <c r="B75" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="C75" s="0" t="s">
         <v>229</v>
-      </c>
-      <c r="C75" s="0" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5506,10 +5552,10 @@
         <v>78</v>
       </c>
       <c r="B76" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="C76" s="0" t="s">
         <v>231</v>
-      </c>
-      <c r="C76" s="0" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5517,10 +5563,10 @@
         <v>78</v>
       </c>
       <c r="B77" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77" s="0" t="s">
         <v>233</v>
-      </c>
-      <c r="C77" s="0" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5528,10 +5574,10 @@
         <v>78</v>
       </c>
       <c r="B78" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="C78" s="0" t="s">
         <v>235</v>
-      </c>
-      <c r="C78" s="0" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5539,10 +5585,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="C79" s="0" t="s">
         <v>237</v>
-      </c>
-      <c r="C79" s="0" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5550,10 +5596,10 @@
         <v>78</v>
       </c>
       <c r="B80" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="C80" s="0" t="s">
         <v>239</v>
-      </c>
-      <c r="C80" s="0" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,10 +5607,10 @@
         <v>78</v>
       </c>
       <c r="B81" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="C81" s="0" t="s">
         <v>241</v>
-      </c>
-      <c r="C81" s="0" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5572,10 +5618,10 @@
         <v>78</v>
       </c>
       <c r="B82" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" s="0" t="s">
         <v>243</v>
-      </c>
-      <c r="C82" s="0" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5583,10 +5629,10 @@
         <v>78</v>
       </c>
       <c r="B83" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="C83" s="0" t="s">
         <v>245</v>
-      </c>
-      <c r="C83" s="0" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5594,10 +5640,10 @@
         <v>78</v>
       </c>
       <c r="B84" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C84" s="0" t="s">
         <v>247</v>
-      </c>
-      <c r="C84" s="0" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5605,10 +5651,10 @@
         <v>78</v>
       </c>
       <c r="B85" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="C85" s="0" t="s">
         <v>249</v>
-      </c>
-      <c r="C85" s="0" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5616,10 +5662,10 @@
         <v>78</v>
       </c>
       <c r="B86" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="C86" s="0" t="s">
         <v>251</v>
-      </c>
-      <c r="C86" s="0" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5627,10 +5673,10 @@
         <v>78</v>
       </c>
       <c r="B87" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C87" s="0" t="s">
         <v>253</v>
-      </c>
-      <c r="C87" s="0" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5638,10 +5684,10 @@
         <v>78</v>
       </c>
       <c r="B88" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="C88" s="0" t="s">
         <v>255</v>
-      </c>
-      <c r="C88" s="0" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5649,10 +5695,10 @@
         <v>78</v>
       </c>
       <c r="B89" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="C89" s="0" t="s">
         <v>257</v>
-      </c>
-      <c r="C89" s="0" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5660,10 +5706,10 @@
         <v>78</v>
       </c>
       <c r="B90" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C90" s="0" t="s">
         <v>259</v>
-      </c>
-      <c r="C90" s="0" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5671,10 +5717,10 @@
         <v>78</v>
       </c>
       <c r="B91" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="C91" s="0" t="s">
         <v>261</v>
-      </c>
-      <c r="C91" s="0" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5682,10 +5728,10 @@
         <v>78</v>
       </c>
       <c r="B92" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="C92" s="0" t="s">
         <v>263</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5693,10 +5739,10 @@
         <v>78</v>
       </c>
       <c r="B93" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="C93" s="0" t="s">
         <v>265</v>
-      </c>
-      <c r="C93" s="0" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5704,10 +5750,10 @@
         <v>78</v>
       </c>
       <c r="B94" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C94" s="0" t="s">
         <v>267</v>
-      </c>
-      <c r="C94" s="0" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5715,10 +5761,10 @@
         <v>78</v>
       </c>
       <c r="B95" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="C95" s="0" t="s">
         <v>269</v>
-      </c>
-      <c r="C95" s="0" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5726,10 +5772,10 @@
         <v>78</v>
       </c>
       <c r="B96" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="C96" s="0" t="s">
         <v>271</v>
-      </c>
-      <c r="C96" s="0" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5737,10 +5783,10 @@
         <v>78</v>
       </c>
       <c r="B97" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="C97" s="0" t="s">
         <v>273</v>
-      </c>
-      <c r="C97" s="0" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5748,10 +5794,10 @@
         <v>78</v>
       </c>
       <c r="B98" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="C98" s="0" t="s">
         <v>275</v>
-      </c>
-      <c r="C98" s="0" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5759,10 +5805,10 @@
         <v>78</v>
       </c>
       <c r="B99" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="C99" s="0" t="s">
         <v>277</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5770,10 +5816,10 @@
         <v>78</v>
       </c>
       <c r="B100" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C100" s="0" t="s">
         <v>279</v>
-      </c>
-      <c r="C100" s="0" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5781,10 +5827,10 @@
         <v>78</v>
       </c>
       <c r="B101" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="C101" s="0" t="s">
         <v>281</v>
-      </c>
-      <c r="C101" s="0" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5792,10 +5838,10 @@
         <v>78</v>
       </c>
       <c r="B102" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="C102" s="0" t="s">
         <v>283</v>
-      </c>
-      <c r="C102" s="0" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5803,10 +5849,10 @@
         <v>78</v>
       </c>
       <c r="B103" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="0" t="s">
         <v>285</v>
-      </c>
-      <c r="C103" s="0" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5814,10 +5860,10 @@
         <v>78</v>
       </c>
       <c r="B104" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="C104" s="0" t="s">
         <v>287</v>
-      </c>
-      <c r="C104" s="0" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5825,10 +5871,10 @@
         <v>78</v>
       </c>
       <c r="B105" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="C105" s="0" t="s">
         <v>289</v>
-      </c>
-      <c r="C105" s="0" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5836,10 +5882,10 @@
         <v>78</v>
       </c>
       <c r="B106" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="C106" s="0" t="s">
         <v>291</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5847,10 +5893,10 @@
         <v>78</v>
       </c>
       <c r="B107" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C107" s="0" t="s">
         <v>293</v>
-      </c>
-      <c r="C107" s="0" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5858,10 +5904,10 @@
         <v>78</v>
       </c>
       <c r="B108" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C108" s="0" t="s">
         <v>295</v>
-      </c>
-      <c r="C108" s="0" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5869,10 +5915,10 @@
         <v>78</v>
       </c>
       <c r="B109" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C109" s="0" t="s">
         <v>297</v>
-      </c>
-      <c r="C109" s="0" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5880,10 +5926,10 @@
         <v>78</v>
       </c>
       <c r="B110" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C110" s="0" t="s">
         <v>299</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5891,10 +5937,10 @@
         <v>78</v>
       </c>
       <c r="B111" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="C111" s="0" t="s">
         <v>301</v>
-      </c>
-      <c r="C111" s="0" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5902,10 +5948,10 @@
         <v>78</v>
       </c>
       <c r="B112" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="C112" s="0" t="s">
         <v>303</v>
-      </c>
-      <c r="C112" s="0" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5913,10 +5959,10 @@
         <v>78</v>
       </c>
       <c r="B113" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="C113" s="0" t="s">
         <v>305</v>
-      </c>
-      <c r="C113" s="0" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5924,10 +5970,10 @@
         <v>78</v>
       </c>
       <c r="B114" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="C114" s="0" t="s">
         <v>307</v>
-      </c>
-      <c r="C114" s="0" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5935,10 +5981,10 @@
         <v>78</v>
       </c>
       <c r="B115" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="C115" s="0" t="s">
         <v>309</v>
-      </c>
-      <c r="C115" s="0" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5946,10 +5992,10 @@
         <v>78</v>
       </c>
       <c r="B116" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="C116" s="0" t="s">
         <v>311</v>
-      </c>
-      <c r="C116" s="0" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5957,10 +6003,10 @@
         <v>78</v>
       </c>
       <c r="B117" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="C117" s="0" t="s">
         <v>313</v>
-      </c>
-      <c r="C117" s="0" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5968,10 +6014,10 @@
         <v>78</v>
       </c>
       <c r="B118" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="C118" s="0" t="s">
         <v>315</v>
-      </c>
-      <c r="C118" s="0" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5979,10 +6025,10 @@
         <v>78</v>
       </c>
       <c r="B119" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="C119" s="0" t="s">
         <v>317</v>
-      </c>
-      <c r="C119" s="0" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5990,10 +6036,10 @@
         <v>78</v>
       </c>
       <c r="B120" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="C120" s="0" t="s">
         <v>319</v>
-      </c>
-      <c r="C120" s="0" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6001,10 +6047,10 @@
         <v>78</v>
       </c>
       <c r="B121" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="C121" s="0" t="s">
         <v>321</v>
-      </c>
-      <c r="C121" s="0" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6012,10 +6058,10 @@
         <v>78</v>
       </c>
       <c r="B122" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="C122" s="0" t="s">
         <v>323</v>
-      </c>
-      <c r="C122" s="0" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6023,10 +6069,10 @@
         <v>78</v>
       </c>
       <c r="B123" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="C123" s="0" t="s">
         <v>325</v>
-      </c>
-      <c r="C123" s="0" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6034,10 +6080,10 @@
         <v>78</v>
       </c>
       <c r="B124" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="C124" s="0" t="s">
         <v>327</v>
-      </c>
-      <c r="C124" s="0" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6045,10 +6091,10 @@
         <v>78</v>
       </c>
       <c r="B125" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="C125" s="0" t="s">
         <v>329</v>
-      </c>
-      <c r="C125" s="0" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6056,10 +6102,10 @@
         <v>78</v>
       </c>
       <c r="B126" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="C126" s="0" t="s">
         <v>331</v>
-      </c>
-      <c r="C126" s="0" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6067,10 +6113,10 @@
         <v>78</v>
       </c>
       <c r="B127" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="C127" s="0" t="s">
         <v>333</v>
-      </c>
-      <c r="C127" s="0" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6078,10 +6124,10 @@
         <v>78</v>
       </c>
       <c r="B128" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="C128" s="0" t="s">
         <v>335</v>
-      </c>
-      <c r="C128" s="0" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6089,6 +6135,9 @@
         <v>74</v>
       </c>
       <c r="B129" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="C129" s="0" t="s">
         <v>337</v>
       </c>
     </row>
@@ -6099,13 +6148,19 @@
       <c r="B130" s="0" t="s">
         <v>338</v>
       </c>
+      <c r="C130" s="0" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
         <v>74</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6113,7 +6168,10 @@
         <v>74</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
+      </c>
+      <c r="C132" s="0" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6121,7 +6179,10 @@
         <v>74</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>341</v>
+        <v>344</v>
+      </c>
+      <c r="C133" s="0" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6129,7 +6190,10 @@
         <v>74</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>342</v>
+        <v>346</v>
+      </c>
+      <c r="C134" s="0" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6137,7 +6201,10 @@
         <v>74</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>343</v>
+        <v>348</v>
+      </c>
+      <c r="C135" s="0" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6145,7 +6212,10 @@
         <v>74</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>344</v>
+        <v>350</v>
+      </c>
+      <c r="C136" s="0" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6153,7 +6223,10 @@
         <v>74</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>345</v>
+        <v>352</v>
+      </c>
+      <c r="C137" s="0" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6161,7 +6234,10 @@
         <v>74</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>346</v>
+        <v>354</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6169,7 +6245,10 @@
         <v>74</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>347</v>
+        <v>356</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6177,7 +6256,10 @@
         <v>74</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>348</v>
+        <v>358</v>
+      </c>
+      <c r="C140" s="0" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6185,7 +6267,10 @@
         <v>74</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>349</v>
+        <v>360</v>
+      </c>
+      <c r="C141" s="0" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6193,7 +6278,10 @@
         <v>74</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>350</v>
+        <v>361</v>
+      </c>
+      <c r="C142" s="0" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6201,7 +6289,10 @@
         <v>74</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>351</v>
+        <v>363</v>
+      </c>
+      <c r="C143" s="0" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6209,7 +6300,10 @@
         <v>74</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>352</v>
+        <v>365</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6217,10 +6311,10 @@
         <v>76</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6228,10 +6322,10 @@
         <v>76</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6239,10 +6333,10 @@
         <v>76</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6250,10 +6344,10 @@
         <v>76</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6261,10 +6355,10 @@
         <v>76</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6272,10 +6366,10 @@
         <v>76</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6283,10 +6377,10 @@
         <v>76</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6294,10 +6388,10 @@
         <v>76</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6305,10 +6399,10 @@
         <v>76</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6316,10 +6410,10 @@
         <v>76</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6327,10 +6421,10 @@
         <v>76</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -6350,43 +6444,43 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N54"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>100</v>
@@ -6412,7 +6506,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>100</v>
@@ -6438,7 +6532,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>100</v>
@@ -6464,7 +6558,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>100</v>
@@ -6490,7 +6584,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>100</v>
@@ -6516,7 +6610,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>100</v>
@@ -6542,7 +6636,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>100</v>
@@ -6568,7 +6662,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>100</v>
@@ -6594,7 +6688,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>100</v>
@@ -6620,7 +6714,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>100</v>
@@ -6646,7 +6740,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>100</v>
@@ -6672,7 +6766,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>100</v>
@@ -6698,7 +6792,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>100</v>
@@ -6724,7 +6818,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>100</v>
@@ -6750,7 +6844,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>100</v>
@@ -6776,7 +6870,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>100</v>
@@ -6802,7 +6896,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>100</v>
@@ -6828,7 +6922,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>100</v>
@@ -6854,7 +6948,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>100</v>
@@ -6880,7 +6974,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>100</v>
@@ -6906,7 +7000,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>100</v>
@@ -6932,7 +7026,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>100</v>
@@ -6958,7 +7052,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>100</v>
@@ -6984,7 +7078,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>100</v>
@@ -7010,46 +7104,46 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7092,31 +7186,31 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7124,7 +7218,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>0</v>
@@ -7150,7 +7244,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>0</v>
@@ -7176,7 +7270,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>0</v>
@@ -7202,7 +7296,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
@@ -7228,7 +7322,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>0</v>
@@ -7254,7 +7348,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0</v>
@@ -7280,7 +7374,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>0</v>
@@ -7306,7 +7400,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0</v>
@@ -7332,7 +7426,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>0</v>
@@ -7358,7 +7452,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>100</v>
@@ -7384,7 +7478,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>100</v>
@@ -7410,7 +7504,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>100</v>
@@ -7436,7 +7530,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="1" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>100</v>
@@ -7462,7 +7556,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>100</v>
@@ -7488,7 +7582,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="1" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>100</v>
@@ -7514,7 +7608,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="1" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>100</v>
@@ -7540,7 +7634,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>100</v>
@@ -7566,7 +7660,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>0</v>
@@ -7592,7 +7686,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>0</v>
@@ -7618,7 +7712,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>0</v>
@@ -7644,7 +7738,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="1" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>0</v>
@@ -7670,7 +7764,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="1" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>0</v>
@@ -7696,7 +7790,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="1" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>0</v>
@@ -7722,7 +7816,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="1" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>0</v>
@@ -7748,46 +7842,46 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7845,43 +7939,43 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>100</v>
@@ -7907,7 +8001,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>100</v>
@@ -7933,7 +8027,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>100</v>
@@ -7959,7 +8053,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>100</v>
@@ -7985,7 +8079,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>100</v>
@@ -8011,7 +8105,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>100</v>
@@ -8037,7 +8131,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>100</v>
@@ -8063,7 +8157,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>100</v>
@@ -8089,7 +8183,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>100</v>
@@ -8115,7 +8209,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>100</v>
@@ -8141,7 +8235,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>100</v>
@@ -8167,7 +8261,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>100</v>
@@ -8193,7 +8287,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>100</v>
@@ -8219,7 +8313,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>100</v>
@@ -8245,7 +8339,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>100</v>
@@ -8271,7 +8365,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>100</v>
@@ -8297,7 +8391,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>100</v>
@@ -8323,7 +8417,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>100</v>
@@ -8349,7 +8443,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>100</v>
@@ -8375,7 +8469,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>100</v>
@@ -8401,7 +8495,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>100</v>
@@ -8427,7 +8521,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>100</v>
@@ -8453,7 +8547,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>100</v>
@@ -8479,7 +8573,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>100</v>
@@ -8505,46 +8599,46 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8602,43 +8696,43 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>100</v>
@@ -8664,7 +8758,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>100</v>
@@ -8690,7 +8784,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>100</v>
@@ -8716,7 +8810,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>100</v>
@@ -8742,7 +8836,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>100</v>
@@ -8768,7 +8862,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>100</v>
@@ -8794,7 +8888,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>100</v>
@@ -8820,7 +8914,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>100</v>
@@ -8846,7 +8940,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>100</v>
@@ -8872,7 +8966,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>100</v>
@@ -8898,7 +8992,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>100</v>
@@ -8924,7 +9018,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>100</v>
@@ -8950,7 +9044,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>100</v>
@@ -8976,7 +9070,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>100</v>
@@ -9002,7 +9096,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>100</v>
@@ -9028,7 +9122,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>100</v>
@@ -9054,7 +9148,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>100</v>
@@ -9080,7 +9174,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>100</v>
@@ -9106,7 +9200,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>100</v>
@@ -9132,7 +9226,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>100</v>
@@ -9158,7 +9252,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>100</v>
@@ -9184,7 +9278,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>100</v>
@@ -9210,7 +9304,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>100</v>
@@ -9236,7 +9330,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>100</v>
@@ -9262,46 +9356,46 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
